--- a/docs/Decodifiche/132_dmnm_dec_stato_invio.xlsx
+++ b/docs/Decodifiche/132_dmnm_dec_stato_invio.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
   <si>
     <t>ID</t>
   </si>
@@ -35,7 +35,7 @@
     <t>ATTESA</t>
   </si>
   <si>
-    <t>2025-10-13 13:58:21.0</t>
+    <t>2025-10-15 10:26:29.0</t>
   </si>
   <si>
     <t>9999-12-31 00:00:00.0</t>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>ERRORE</t>
-  </si>
-  <si>
-    <t>2025-10-13 13:58:22.0</t>
   </si>
 </sst>
 </file>
@@ -181,7 +178,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
